--- a/pipelines/Demo_data/Output_data/out_Планшетный компьютер Apple iPad.xlsx
+++ b/pipelines/Demo_data/Output_data/out_Планшетный компьютер Apple iPad.xlsx
@@ -486,10 +486,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F2" t="n">
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -530,10 +528,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F3" t="n">
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -574,10 +570,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F4" t="n">
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -618,10 +612,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F5" t="n">
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -662,10 +654,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -706,10 +696,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F7" t="n">
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -750,10 +738,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F8" t="n">
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -794,10 +780,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -838,10 +822,8 @@
           <t>114**********</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>250536.54</t>
-        </is>
+      <c r="F10" t="n">
+        <v>250536.54</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -882,10 +864,8 @@
           <t>114**********</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>15761.87</t>
-        </is>
+      <c r="F11" t="n">
+        <v>15761.87</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,10 +906,8 @@
           <t>114**********</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>258377.2</t>
-        </is>
+      <c r="F12" t="n">
+        <v>258377.2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -970,10 +948,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>7338.85</t>
-        </is>
+      <c r="F13" t="n">
+        <v>7338.85</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1014,10 +990,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F14" t="n">
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1058,10 +1032,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>28004.37</t>
-        </is>
+      <c r="F15" t="n">
+        <v>28004.37</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1102,10 +1074,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>40275</t>
-        </is>
+      <c r="F16" t="n">
+        <v>40275</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1146,10 +1116,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>168432.17</t>
-        </is>
+      <c r="F17" t="n">
+        <v>168432.17</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1190,10 +1158,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>58264.84</t>
-        </is>
+      <c r="F18" t="n">
+        <v>58264.84</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1234,10 +1200,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>14671.84</t>
-        </is>
+      <c r="F19" t="n">
+        <v>14671.84</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1278,10 +1242,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>294660.5</t>
-        </is>
+      <c r="F20" t="n">
+        <v>294660.5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1322,10 +1284,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>182818.41</t>
-        </is>
+      <c r="F21" t="n">
+        <v>182818.41</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1366,10 +1326,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>51575.57</t>
-        </is>
+      <c r="F22" t="n">
+        <v>51575.57</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1410,10 +1368,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>166675.77</t>
-        </is>
+      <c r="F23" t="n">
+        <v>166675.77</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1454,10 +1410,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>49353.37</t>
-        </is>
+      <c r="F24" t="n">
+        <v>49353.37</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1498,10 +1452,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>63706.69</t>
-        </is>
+      <c r="F25" t="n">
+        <v>63706.69</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1542,10 +1494,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>35255.12</t>
-        </is>
+      <c r="F26" t="n">
+        <v>35255.12</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1586,10 +1536,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>45033.1</t>
-        </is>
+      <c r="F27" t="n">
+        <v>45033.1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1630,10 +1578,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>84927.43</t>
-        </is>
+      <c r="F28" t="n">
+        <v>84927.42999999999</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1674,10 +1620,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>163391.03</t>
-        </is>
+      <c r="F29" t="n">
+        <v>163391.03</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1718,10 +1662,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>108941.88</t>
-        </is>
+      <c r="F30" t="n">
+        <v>108941.88</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1762,10 +1704,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>144962.18</t>
-        </is>
+      <c r="F31" t="n">
+        <v>144962.18</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1806,10 +1746,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>117168.21</t>
-        </is>
+      <c r="F32" t="n">
+        <v>117168.21</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1850,10 +1788,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>85105.92</t>
-        </is>
+      <c r="F33" t="n">
+        <v>85105.92</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1894,10 +1830,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>23766.39</t>
-        </is>
+      <c r="F34" t="n">
+        <v>23766.39</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1938,10 +1872,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>60233.76</t>
-        </is>
+      <c r="F35" t="n">
+        <v>60233.76</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1982,10 +1914,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>138478.45</t>
-        </is>
+      <c r="F36" t="n">
+        <v>138478.45</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2026,10 +1956,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>37291.3</t>
-        </is>
+      <c r="F37" t="n">
+        <v>37291.3</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2070,10 +1998,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F38" t="n">
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2114,10 +2040,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F39" t="n">
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2158,10 +2082,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F40" t="n">
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2202,10 +2124,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>216499.86</t>
-        </is>
+      <c r="F41" t="n">
+        <v>216499.86</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2246,10 +2166,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>157019.56</t>
-        </is>
+      <c r="F42" t="n">
+        <v>157019.56</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2290,10 +2208,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>97797.38</t>
-        </is>
+      <c r="F43" t="n">
+        <v>97797.38</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2334,10 +2250,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F44" t="n">
+        <v>0</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2378,10 +2292,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>161947.75</t>
-        </is>
+      <c r="F45" t="n">
+        <v>161947.75</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2422,10 +2334,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>68444.74</t>
-        </is>
+      <c r="F46" t="n">
+        <v>68444.74000000001</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2466,10 +2376,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>91949.53</t>
-        </is>
+      <c r="F47" t="n">
+        <v>91949.53</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2510,10 +2418,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F48" t="n">
+        <v>0</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2554,10 +2460,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>856.01</t>
-        </is>
+      <c r="F49" t="n">
+        <v>856.01</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2598,10 +2502,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>856.01</t>
-        </is>
+      <c r="F50" t="n">
+        <v>856.01</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2642,10 +2544,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F51" t="n">
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2686,10 +2586,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>930.26</t>
-        </is>
+      <c r="F52" t="n">
+        <v>930.26</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2730,10 +2628,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>930.26</t>
-        </is>
+      <c r="F53" t="n">
+        <v>930.26</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2774,10 +2670,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F54" t="n">
+        <v>0</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2818,10 +2712,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F55" t="n">
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2862,10 +2754,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>875.87</t>
-        </is>
+      <c r="F56" t="n">
+        <v>875.87</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2906,10 +2796,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F57" t="n">
+        <v>0</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2950,10 +2838,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F58" t="n">
+        <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2994,10 +2880,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F59" t="n">
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3038,10 +2922,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F60" t="n">
+        <v>0</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3082,10 +2964,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F61" t="n">
+        <v>0</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3126,10 +3006,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F62" t="n">
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3170,10 +3048,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F63" t="n">
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3214,10 +3090,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F64" t="n">
+        <v>0</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3258,10 +3132,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F65" t="n">
+        <v>0</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3302,10 +3174,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F66" t="n">
+        <v>0</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3346,10 +3216,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F67" t="n">
+        <v>0</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3390,10 +3258,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F68" t="n">
+        <v>0</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3434,10 +3300,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F69" t="n">
+        <v>0</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3478,10 +3342,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F70" t="n">
+        <v>0</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3522,10 +3384,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F71" t="n">
+        <v>0</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3566,10 +3426,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F72" t="n">
+        <v>0</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3610,10 +3468,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F73" t="n">
+        <v>0</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3654,10 +3510,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F74" t="n">
+        <v>0</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3698,10 +3552,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F75" t="n">
+        <v>0</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3742,10 +3594,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F76" t="n">
+        <v>0</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3786,10 +3636,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F77" t="n">
+        <v>0</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3830,10 +3678,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F78" t="n">
+        <v>0</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3874,10 +3720,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F79" t="n">
+        <v>0</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3918,10 +3762,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F80" t="n">
+        <v>0</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3962,10 +3804,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F81" t="n">
+        <v>0</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4006,10 +3846,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F82" t="n">
+        <v>0</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4050,10 +3888,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F83" t="n">
+        <v>0</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4094,10 +3930,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F84" t="n">
+        <v>0</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4138,10 +3972,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F85" t="n">
+        <v>0</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4182,10 +4014,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F86" t="n">
+        <v>0</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4226,10 +4056,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F87" t="n">
+        <v>0</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4270,10 +4098,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F88" t="n">
+        <v>0</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4314,10 +4140,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F89" t="n">
+        <v>0</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4358,10 +4182,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F90" t="n">
+        <v>0</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4402,10 +4224,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F91" t="n">
+        <v>0</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4446,10 +4266,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F92" t="n">
+        <v>0</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4490,10 +4308,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F93" t="n">
+        <v>0</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4534,10 +4350,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F94" t="n">
+        <v>0</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4578,10 +4392,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F95" t="n">
+        <v>0</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4622,10 +4434,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F96" t="n">
+        <v>0</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4666,10 +4476,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F97" t="n">
+        <v>0</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4710,10 +4518,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F98" t="n">
+        <v>0</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4754,10 +4560,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F99" t="n">
+        <v>0</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4798,10 +4602,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F100" t="n">
+        <v>0</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4842,10 +4644,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F101" t="n">
+        <v>0</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4886,10 +4686,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F102" t="n">
+        <v>0</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4930,10 +4728,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F103" t="n">
+        <v>0</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4974,10 +4770,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F104" t="n">
+        <v>0</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5018,10 +4812,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F105" t="n">
+        <v>0</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5062,10 +4854,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F106" t="n">
+        <v>0</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5106,10 +4896,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F107" t="n">
+        <v>0</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5150,10 +4938,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F108" t="n">
+        <v>0</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5194,10 +4980,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F109" t="n">
+        <v>0</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -5238,10 +5022,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F110" t="n">
+        <v>0</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -5282,10 +5064,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F111" t="n">
+        <v>0</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -5326,10 +5106,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F112" t="n">
+        <v>0</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -5370,10 +5148,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F113" t="n">
+        <v>0</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -5414,10 +5190,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F114" t="n">
+        <v>0</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -5458,10 +5232,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F115" t="n">
+        <v>0</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -5502,10 +5274,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F116" t="n">
+        <v>0</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -5546,10 +5316,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F117" t="n">
+        <v>0</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -5590,10 +5358,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F118" t="n">
+        <v>0</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -5634,10 +5400,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F119" t="n">
+        <v>0</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -5678,10 +5442,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F120" t="n">
+        <v>0</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -5722,10 +5484,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F121" t="n">
+        <v>0</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5766,10 +5526,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F122" t="n">
+        <v>0</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -5810,10 +5568,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F123" t="n">
+        <v>0</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -5854,10 +5610,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F124" t="n">
+        <v>0</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>

--- a/pipelines/Demo_data/Output_data/out_Планшетный компьютер Apple iPad.xlsx
+++ b/pipelines/Demo_data/Output_data/out_Планшетный компьютер Apple iPad.xlsx
@@ -486,8 +486,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -528,8 +530,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -570,8 +574,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -612,8 +618,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -654,8 +662,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -696,8 +706,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -738,8 +750,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -780,8 +794,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -822,8 +838,10 @@
           <t>114**********</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>250536.54</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>250536.54</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -864,8 +882,10 @@
           <t>114**********</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>15761.87</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>15761.87</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -906,8 +926,10 @@
           <t>114**********</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>258377.2</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>258377.2</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -948,8 +970,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>7338.85</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>7338.85</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -990,8 +1014,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1032,8 +1058,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>28004.37</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>28004.37</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1074,8 +1102,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>40275</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>40275</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1116,8 +1146,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>168432.17</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>168432.17</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1158,8 +1190,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>58264.84</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>58264.84</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1200,8 +1234,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>14671.84</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>14671.84</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1242,8 +1278,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>294660.5</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>294660.5</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1284,8 +1322,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>182818.41</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>182818.41</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1326,8 +1366,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>51575.57</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>51575.57</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1368,8 +1410,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>166675.77</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>166675.77</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1410,8 +1454,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>49353.37</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>49353.37</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1452,8 +1498,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>63706.69</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>63706.69</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1494,8 +1542,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>35255.12</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>35255.12</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1536,8 +1586,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>45033.1</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>45033.1</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1578,8 +1630,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>84927.42999999999</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>84927.43</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1620,8 +1674,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>163391.03</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>163391.03</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1662,8 +1718,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>108941.88</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>108941.88</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1704,8 +1762,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>144962.18</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>144962.18</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1746,8 +1806,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>117168.21</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>117168.21</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1788,8 +1850,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>85105.92</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>85105.92</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1830,8 +1894,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>23766.39</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>23766.39</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1872,8 +1938,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>60233.76</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>60233.76</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1914,8 +1982,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>138478.45</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>138478.45</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1956,8 +2026,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>37291.3</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>37291.3</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1998,8 +2070,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2040,8 +2114,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2082,8 +2158,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>0</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2124,8 +2202,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>216499.86</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>216499.86</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2166,8 +2246,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>157019.56</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>157019.56</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2208,8 +2290,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>97797.38</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>97797.38</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2250,8 +2334,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2292,8 +2378,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>161947.75</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>161947.75</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2334,8 +2422,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>68444.74000000001</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>68444.74</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2376,8 +2466,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>91949.53</v>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>91949.53</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2418,8 +2510,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>0</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2460,8 +2554,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>856.01</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>856.01</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2502,8 +2598,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>856.01</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>856.01</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2544,8 +2642,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>0</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2586,8 +2686,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v>930.26</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>930.26</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2628,8 +2730,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>930.26</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>930.26</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2670,8 +2774,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>0</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2712,8 +2818,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>0</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2754,8 +2862,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v>875.87</v>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>875.87</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2796,8 +2906,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>0</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2838,8 +2950,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>0</v>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2880,8 +2994,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v>0</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2922,8 +3038,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>0</v>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2964,8 +3082,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>0</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3006,8 +3126,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v>0</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3048,8 +3170,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>0</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3090,8 +3214,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>0</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3132,8 +3258,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F65" t="n">
-        <v>0</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3174,8 +3302,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>0</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3216,8 +3346,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>0</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3258,8 +3390,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F68" t="n">
-        <v>0</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3300,8 +3434,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>0</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3342,8 +3478,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>0</v>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3384,8 +3522,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>0</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3426,8 +3566,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>0</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3468,8 +3610,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>0</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3510,8 +3654,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F74" t="n">
-        <v>0</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3552,8 +3698,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>0</v>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3594,8 +3742,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>0</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3636,8 +3786,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F77" t="n">
-        <v>0</v>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3678,8 +3830,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>0</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3720,8 +3874,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>0</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3762,8 +3918,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F80" t="n">
-        <v>0</v>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3804,8 +3962,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F81" t="n">
-        <v>0</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3846,8 +4006,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F82" t="n">
-        <v>0</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3888,8 +4050,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F83" t="n">
-        <v>0</v>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3930,8 +4094,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F84" t="n">
-        <v>0</v>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3972,8 +4138,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F85" t="n">
-        <v>0</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4014,8 +4182,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F86" t="n">
-        <v>0</v>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4056,8 +4226,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F87" t="n">
-        <v>0</v>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4098,8 +4270,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F88" t="n">
-        <v>0</v>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4140,8 +4314,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F89" t="n">
-        <v>0</v>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4182,8 +4358,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F90" t="n">
-        <v>0</v>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4224,8 +4402,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F91" t="n">
-        <v>0</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4266,8 +4446,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F92" t="n">
-        <v>0</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4308,8 +4490,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>0</v>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4350,8 +4534,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F94" t="n">
-        <v>0</v>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4392,8 +4578,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F95" t="n">
-        <v>0</v>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4434,8 +4622,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4476,8 +4666,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F97" t="n">
-        <v>0</v>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4518,8 +4710,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F98" t="n">
-        <v>0</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4560,8 +4754,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F99" t="n">
-        <v>0</v>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4602,8 +4798,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F100" t="n">
-        <v>0</v>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4644,8 +4842,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F101" t="n">
-        <v>0</v>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4686,8 +4886,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F102" t="n">
-        <v>0</v>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4728,8 +4930,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F103" t="n">
-        <v>0</v>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4770,8 +4974,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F104" t="n">
-        <v>0</v>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4812,8 +5018,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F105" t="n">
-        <v>0</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4854,8 +5062,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F106" t="n">
-        <v>0</v>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4896,8 +5106,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F107" t="n">
-        <v>0</v>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4938,8 +5150,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F108" t="n">
-        <v>0</v>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4980,8 +5194,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F109" t="n">
-        <v>0</v>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -5022,8 +5238,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F110" t="n">
-        <v>0</v>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -5064,8 +5282,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F111" t="n">
-        <v>0</v>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -5106,8 +5326,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F112" t="n">
-        <v>0</v>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -5148,8 +5370,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F113" t="n">
-        <v>0</v>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -5190,8 +5414,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F114" t="n">
-        <v>0</v>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -5232,8 +5458,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F115" t="n">
-        <v>0</v>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -5274,8 +5502,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F116" t="n">
-        <v>0</v>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -5316,8 +5546,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F117" t="n">
-        <v>0</v>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -5358,8 +5590,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F118" t="n">
-        <v>0</v>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -5400,8 +5634,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F119" t="n">
-        <v>0</v>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -5442,8 +5678,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F120" t="n">
-        <v>0</v>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -5484,8 +5722,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F121" t="n">
-        <v>0</v>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5526,8 +5766,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F122" t="n">
-        <v>0</v>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -5568,8 +5810,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F123" t="n">
-        <v>0</v>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -5610,8 +5854,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F124" t="n">
-        <v>0</v>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
